--- a/IzlocilniBoji/SP 2026 - izlocilni.xlsx
+++ b/IzlocilniBoji/SP 2026 - izlocilni.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rihar\Documents\SP2026\IzlocilniBoji\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34D499A-0F31-4222-9E27-F581DB12C1C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41E3802-E688-4F52-A939-A34217344E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="zakljucni boji" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="105">
   <si>
     <t>Zaključni  boji</t>
   </si>
@@ -731,12 +731,81 @@
   <si>
     <t>SLONOK. O.</t>
   </si>
+  <si>
+    <t>NIZOZEMSKA</t>
+  </si>
+  <si>
+    <t>JAPONSKA</t>
+  </si>
+  <si>
+    <t>AVSTRALIJA</t>
+  </si>
+  <si>
+    <t>PARAGVAJ</t>
+  </si>
+  <si>
+    <t>FRANCIJA</t>
+  </si>
+  <si>
+    <t>ŠVEDSKA</t>
+  </si>
+  <si>
+    <t>ŠPANIJA</t>
+  </si>
+  <si>
+    <t>BIH</t>
+  </si>
+  <si>
+    <t>BELGIJA</t>
+  </si>
+  <si>
+    <t>NORVEŠKA</t>
+  </si>
+  <si>
+    <t>ZELENORTSK. O.</t>
+  </si>
+  <si>
+    <t>EGIPT</t>
+  </si>
+  <si>
+    <t>PORTUGALSKA</t>
+  </si>
+  <si>
+    <t>HRVAŠKA</t>
+  </si>
+  <si>
+    <t>AVSTRIJA</t>
+  </si>
+  <si>
+    <t>SENEGAL</t>
+  </si>
+  <si>
+    <t>EKVADOR</t>
+  </si>
+  <si>
+    <t>ANGLIJA</t>
+  </si>
+  <si>
+    <t>DR KONGO</t>
+  </si>
+  <si>
+    <t>ALŽIRIJA</t>
+  </si>
+  <si>
+    <t>KOLUMBIJA</t>
+  </si>
+  <si>
+    <t>GANA</t>
+  </si>
+  <si>
+    <t>Boštjan Prevc</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -946,13 +1015,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="3" tint="-0.499984740745262"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF0070C0"/>
       <name val="Calibri"/>
@@ -1009,6 +1071,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="3" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1018,7 +1104,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -1084,21 +1170,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color theme="5" tint="-0.24994659260841701"/>
-      </left>
-      <right style="double">
-        <color theme="5" tint="-0.24994659260841701"/>
-      </right>
-      <top style="medium">
-        <color theme="5" tint="-0.24994659260841701"/>
-      </top>
-      <bottom style="medium">
-        <color theme="5" tint="-0.24994659260841701"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color theme="5" tint="-0.24994659260841701"/>
       </left>
@@ -1110,21 +1181,6 @@
       </top>
       <bottom style="medium">
         <color theme="5" tint="-0.24994659260841701"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="9" tint="-0.24994659260841701"/>
-      </left>
-      <right style="double">
-        <color theme="9" tint="-0.24994659260841701"/>
-      </right>
-      <top style="medium">
-        <color theme="9" tint="-0.24994659260841701"/>
-      </top>
-      <bottom style="medium">
-        <color theme="9" tint="-0.24994659260841701"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1356,52 +1412,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="double">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="double">
-        <color auto="1"/>
-      </right>
-      <top style="double">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="double">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom style="double">
         <color auto="1"/>
@@ -1490,7 +1502,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1513,22 +1525,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1558,6 +1564,83 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1567,109 +1650,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1679,110 +1662,95 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2118,182 +2086,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="59"/>
-      <c r="R1" s="59"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
     </row>
     <row r="2" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+      <c r="R2" s="84"/>
     </row>
     <row r="3" spans="1:25" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="60" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="T3" s="60"/>
-      <c r="U3" s="61"/>
-      <c r="V3" s="61"/>
-      <c r="W3" s="61"/>
-      <c r="X3" s="61"/>
-      <c r="Y3" s="61"/>
+      <c r="T3" s="84"/>
+      <c r="U3" s="85" t="s">
+        <v>104</v>
+      </c>
+      <c r="V3" s="85"/>
+      <c r="W3" s="85"/>
+      <c r="X3" s="85"/>
+      <c r="Y3" s="85"/>
     </row>
     <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
     </row>
     <row r="5" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
     </row>
     <row r="6" spans="1:25" ht="10.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="66"/>
-      <c r="E7" s="57" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="57"/>
-      <c r="H7" s="58" t="s">
+      <c r="C7" s="87"/>
+      <c r="E7" s="80" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="80"/>
+      <c r="H7" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="I7" s="58"/>
-      <c r="K7" s="62" t="s">
+      <c r="I7" s="81"/>
+      <c r="K7" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="L7" s="62"/>
-      <c r="M7" s="62"/>
-      <c r="O7" s="62" t="s">
+      <c r="L7" s="86"/>
+      <c r="M7" s="86"/>
+      <c r="O7" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="P7" s="62"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="62"/>
-      <c r="T7" s="75" t="s">
+      <c r="P7" s="86"/>
+      <c r="Q7" s="86"/>
+      <c r="R7" s="86"/>
+      <c r="T7" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="U7" s="75"/>
-      <c r="V7" s="75"/>
+      <c r="U7" s="45"/>
+      <c r="V7" s="45"/>
     </row>
     <row r="8" spans="1:25" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="T8" s="79"/>
-      <c r="U8" s="79"/>
-      <c r="V8" s="79"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15"/>
+      <c r="T8" s="15"/>
+      <c r="U8" s="15"/>
+      <c r="V8" s="15"/>
     </row>
     <row r="9" spans="1:25" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="T9" s="76"/>
-      <c r="U9" s="76"/>
-      <c r="V9" s="76"/>
+      <c r="C9" s="11">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:25" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="1"/>
       <c r="D10" s="4"/>
-      <c r="T10" s="76"/>
-      <c r="U10" s="76"/>
-      <c r="V10" s="76"/>
     </row>
     <row r="11" spans="1:25" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="14"/>
-      <c r="T11" s="76"/>
-      <c r="U11" s="82">
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="E11" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="12">
+        <v>1</v>
+      </c>
+      <c r="U11" s="24">
         <v>3</v>
       </c>
-      <c r="V11" s="76"/>
     </row>
     <row r="12" spans="1:25" ht="9.9499999999999993" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="1"/>
@@ -2301,76 +2269,98 @@
       <c r="E12" s="6">
         <v>2</v>
       </c>
-      <c r="G12" s="36"/>
-      <c r="T12" s="88"/>
-      <c r="U12" s="89"/>
-      <c r="V12" s="92"/>
+      <c r="G12" s="53"/>
+      <c r="T12" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="U12" s="42"/>
+      <c r="V12" s="47">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" spans="1:25" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="13"/>
+      <c r="B13" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="11">
+        <v>0</v>
+      </c>
       <c r="D13" s="2"/>
-      <c r="G13" s="36"/>
-      <c r="T13" s="90"/>
-      <c r="U13" s="91"/>
-      <c r="V13" s="93"/>
+      <c r="G13" s="53"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="44"/>
+      <c r="V13" s="48"/>
     </row>
     <row r="14" spans="1:25" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="25"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="15"/>
-      <c r="T14" s="94" t="s">
+      <c r="F14" s="50"/>
+      <c r="H14" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="I14" s="13">
+        <v>2</v>
+      </c>
+      <c r="T14" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="U14" s="94"/>
-      <c r="V14" s="94"/>
+      <c r="U14" s="49"/>
+      <c r="V14" s="49"/>
     </row>
     <row r="15" spans="1:25" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="13"/>
+      <c r="B15" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="11">
+        <v>3</v>
+      </c>
       <c r="D15" s="2"/>
       <c r="E15" s="5"/>
-      <c r="G15" s="27"/>
+      <c r="G15" s="52"/>
       <c r="H15" s="7">
         <v>2</v>
       </c>
-      <c r="J15" s="36"/>
-      <c r="T15" s="88"/>
-      <c r="U15" s="89"/>
-      <c r="V15" s="92"/>
+      <c r="J15" s="53"/>
+      <c r="T15" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="U15" s="42"/>
+      <c r="V15" s="47">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:25" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="1"/>
       <c r="D16" s="4"/>
-      <c r="G16" s="27"/>
-      <c r="J16" s="36"/>
-      <c r="T16" s="90"/>
-      <c r="U16" s="91"/>
-      <c r="V16" s="93"/>
+      <c r="G16" s="52"/>
+      <c r="J16" s="53"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="44"/>
+      <c r="V16" s="48"/>
     </row>
     <row r="17" spans="1:22" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="14"/>
-      <c r="J17" s="36"/>
-      <c r="T17" s="76"/>
-      <c r="U17" s="78">
+      <c r="B17" s="50"/>
+      <c r="C17" s="50"/>
+      <c r="E17" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" s="12">
+        <v>2</v>
+      </c>
+      <c r="J17" s="53"/>
+      <c r="U17" s="7">
         <v>3</v>
       </c>
-      <c r="V17" s="76"/>
     </row>
     <row r="18" spans="1:22" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1"/>
@@ -2378,95 +2368,102 @@
       <c r="E18" s="6">
         <v>2</v>
       </c>
-      <c r="J18" s="36"/>
-      <c r="T18" s="76"/>
-      <c r="U18" s="76"/>
-      <c r="V18" s="76"/>
+      <c r="J18" s="53"/>
     </row>
     <row r="19" spans="1:22" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="13"/>
+      <c r="B19" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="11">
+        <v>1</v>
+      </c>
       <c r="D19" s="2"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="54"/>
-      <c r="N19" s="18"/>
-      <c r="T19" s="76"/>
-      <c r="U19" s="75" t="s">
+      <c r="K19" s="74" t="s">
+        <v>86</v>
+      </c>
+      <c r="L19" s="75"/>
+      <c r="M19" s="71">
+        <v>2</v>
+      </c>
+      <c r="N19" s="16"/>
+      <c r="U19" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="V19" s="75"/>
+      <c r="V19" s="45"/>
     </row>
     <row r="20" spans="1:22" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G20" s="25" t="s">
+      <c r="G20" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="51"/>
-      <c r="M20" s="55"/>
-      <c r="N20" s="18"/>
-      <c r="T20" s="76"/>
-      <c r="U20" s="87"/>
-      <c r="V20" s="87"/>
-    </row>
-    <row r="21" spans="1:22" ht="9.9499999999999993" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="K21" s="50"/>
-      <c r="L21" s="51"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="18"/>
-      <c r="T21" s="76"/>
-      <c r="U21" s="83"/>
-      <c r="V21" s="84"/>
-    </row>
-    <row r="22" spans="1:22" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="22" t="s">
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="K20" s="76"/>
+      <c r="L20" s="77"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="16"/>
+      <c r="U20" s="46"/>
+      <c r="V20" s="46"/>
+    </row>
+    <row r="21" spans="1:22" ht="9.9499999999999993" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="K21" s="76"/>
+      <c r="L21" s="77"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="16"/>
+      <c r="U21" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="V21" s="42"/>
+    </row>
+    <row r="22" spans="1:22" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="13"/>
+      <c r="C22" s="11">
+        <v>1</v>
+      </c>
       <c r="D22" s="2"/>
-      <c r="K22" s="52"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="56"/>
-      <c r="N22" s="18"/>
-      <c r="T22" s="76"/>
-      <c r="U22" s="85"/>
-      <c r="V22" s="86"/>
+      <c r="K22" s="78"/>
+      <c r="L22" s="79"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="16"/>
+      <c r="U22" s="43"/>
+      <c r="V22" s="44"/>
     </row>
     <row r="23" spans="1:22" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1"/>
       <c r="D23" s="4"/>
-      <c r="J23" s="27"/>
+      <c r="J23" s="52"/>
       <c r="L23" s="6">
         <v>3</v>
       </c>
-      <c r="N23" s="36"/>
-      <c r="T23" s="76"/>
-      <c r="U23" s="76"/>
-      <c r="V23" s="77">
+      <c r="N23" s="53"/>
+      <c r="V23" s="6">
         <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="14"/>
-      <c r="J24" s="27"/>
-      <c r="N24" s="36"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="50"/>
+      <c r="E24" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="12">
+        <v>1</v>
+      </c>
+      <c r="J24" s="52"/>
+      <c r="N24" s="53"/>
     </row>
     <row r="25" spans="1:22" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="1"/>
@@ -2474,63 +2471,77 @@
       <c r="E25" s="6">
         <v>2</v>
       </c>
-      <c r="G25" s="36"/>
-      <c r="J25" s="27"/>
-      <c r="N25" s="36"/>
+      <c r="G25" s="53"/>
+      <c r="J25" s="52"/>
+      <c r="N25" s="53"/>
     </row>
     <row r="26" spans="1:22" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="13"/>
+      <c r="C26" s="11">
+        <v>1</v>
+      </c>
       <c r="D26" s="2"/>
-      <c r="G26" s="36"/>
-      <c r="J26" s="27"/>
-      <c r="N26" s="36"/>
+      <c r="G26" s="53"/>
+      <c r="J26" s="52"/>
+      <c r="N26" s="53"/>
     </row>
     <row r="27" spans="1:22" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E27" s="25" t="s">
+      <c r="E27" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="F27" s="25"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="15"/>
-      <c r="N27" s="36"/>
+      <c r="F27" s="50"/>
+      <c r="H27" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="I27" s="13">
+        <v>1</v>
+      </c>
+      <c r="N27" s="53"/>
     </row>
     <row r="28" spans="1:22" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="13"/>
+      <c r="B28" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="11">
+        <v>2</v>
+      </c>
       <c r="D28" s="2"/>
-      <c r="G28" s="27"/>
+      <c r="G28" s="52"/>
       <c r="H28" s="7">
         <v>2</v>
       </c>
-      <c r="N28" s="36"/>
+      <c r="N28" s="53"/>
     </row>
     <row r="29" spans="1:22" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
       <c r="D29" s="4"/>
-      <c r="G29" s="27"/>
-      <c r="N29" s="36"/>
+      <c r="G29" s="52"/>
+      <c r="N29" s="53"/>
     </row>
     <row r="30" spans="1:22" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="14"/>
-      <c r="N30" s="36"/>
-      <c r="O30" s="46"/>
-      <c r="P30" s="46"/>
-      <c r="Q30" s="46"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="E30" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="F30" s="12">
+        <v>2</v>
+      </c>
+      <c r="N30" s="53"/>
+      <c r="O30" s="66"/>
+      <c r="P30" s="66"/>
+      <c r="Q30" s="66"/>
     </row>
     <row r="31" spans="1:22" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="1"/>
@@ -2538,64 +2549,78 @@
       <c r="E31" s="6">
         <v>2</v>
       </c>
-      <c r="N31" s="36"/>
+      <c r="N31" s="53"/>
     </row>
     <row r="32" spans="1:22" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="13"/>
+      <c r="C32" s="11">
+        <v>1</v>
+      </c>
       <c r="D32" s="2"/>
-      <c r="O32" s="67"/>
+      <c r="O32" s="67" t="s">
+        <v>86</v>
+      </c>
       <c r="P32" s="67"/>
       <c r="Q32" s="67"/>
-      <c r="R32" s="68"/>
+      <c r="R32" s="27">
+        <v>2</v>
+      </c>
     </row>
     <row r="33" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K33" s="102" t="s">
+      <c r="K33" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="L33" s="102"/>
-      <c r="M33" s="102"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="69"/>
-      <c r="P33" s="69"/>
-      <c r="Q33" s="69"/>
-      <c r="R33" s="70"/>
+      <c r="L33" s="70"/>
+      <c r="M33" s="70"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="68"/>
+      <c r="P33" s="68"/>
+      <c r="Q33" s="68"/>
+      <c r="R33" s="28"/>
     </row>
     <row r="34" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="O34" s="71"/>
-      <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
-      <c r="R34" s="72"/>
+      <c r="B34" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="11">
+        <v>2</v>
+      </c>
+      <c r="O34" s="69"/>
+      <c r="P34" s="69"/>
+      <c r="Q34" s="69"/>
+      <c r="R34" s="29"/>
     </row>
     <row r="35" spans="1:19" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1"/>
       <c r="D35" s="4"/>
-      <c r="N35" s="47"/>
+      <c r="N35" s="40"/>
       <c r="Q35" s="6">
-        <v>8</v>
-      </c>
-      <c r="S35" s="36"/>
+        <v>5</v>
+      </c>
+      <c r="S35" s="53"/>
     </row>
     <row r="36" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="25" t="s">
+      <c r="A36" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="14"/>
-      <c r="N36" s="47"/>
-      <c r="S36" s="36"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="E36" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="12">
+        <v>1</v>
+      </c>
+      <c r="N36" s="40"/>
+      <c r="S36" s="53"/>
     </row>
     <row r="37" spans="1:19" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="1"/>
@@ -2603,69 +2628,85 @@
       <c r="E37" s="6">
         <v>2</v>
       </c>
-      <c r="G37" s="36"/>
-      <c r="N37" s="47"/>
-      <c r="S37" s="36"/>
+      <c r="G37" s="53"/>
+      <c r="N37" s="40"/>
+      <c r="S37" s="53"/>
     </row>
     <row r="38" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="23"/>
-      <c r="C38" s="13"/>
+      <c r="B38" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" s="11">
+        <v>0</v>
+      </c>
       <c r="D38" s="2"/>
-      <c r="G38" s="36"/>
-      <c r="N38" s="47"/>
-      <c r="S38" s="36"/>
+      <c r="G38" s="53"/>
+      <c r="N38" s="40"/>
+      <c r="S38" s="53"/>
     </row>
     <row r="39" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
-      <c r="E39" s="25" t="s">
+      <c r="E39" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F39" s="26"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="15"/>
-      <c r="N39" s="47"/>
-      <c r="S39" s="36"/>
+      <c r="F39" s="51"/>
+      <c r="H39" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="I39" s="13">
+        <v>2</v>
+      </c>
+      <c r="N39" s="40"/>
+      <c r="S39" s="53"/>
     </row>
     <row r="40" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="22" t="s">
+      <c r="A40" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="13"/>
+      <c r="B40" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="11">
+        <v>2</v>
+      </c>
       <c r="D40" s="2"/>
       <c r="E40" s="5"/>
-      <c r="G40" s="27"/>
+      <c r="G40" s="52"/>
       <c r="H40" s="7">
         <v>2</v>
       </c>
-      <c r="J40" s="36"/>
-      <c r="N40" s="47"/>
-      <c r="S40" s="36"/>
+      <c r="J40" s="53"/>
+      <c r="N40" s="40"/>
+      <c r="S40" s="53"/>
     </row>
     <row r="41" spans="1:19" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="1"/>
       <c r="D41" s="4"/>
-      <c r="G41" s="27"/>
-      <c r="J41" s="36"/>
-      <c r="N41" s="47"/>
-      <c r="S41" s="36"/>
+      <c r="G41" s="52"/>
+      <c r="J41" s="53"/>
+      <c r="N41" s="40"/>
+      <c r="S41" s="53"/>
     </row>
     <row r="42" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="14"/>
-      <c r="J42" s="36"/>
-      <c r="N42" s="47"/>
-      <c r="S42" s="36"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="51"/>
+      <c r="E42" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="F42" s="12">
+        <v>2</v>
+      </c>
+      <c r="J42" s="53"/>
+      <c r="N42" s="40"/>
+      <c r="S42" s="53"/>
     </row>
     <row r="43" spans="1:19" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="1"/>
@@ -2673,77 +2714,91 @@
       <c r="E43" s="6">
         <v>2</v>
       </c>
-      <c r="J43" s="36"/>
-      <c r="N43" s="47"/>
-      <c r="S43" s="36"/>
+      <c r="J43" s="53"/>
+      <c r="N43" s="40"/>
+      <c r="S43" s="53"/>
     </row>
     <row r="44" spans="1:19" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="22" t="s">
+      <c r="A44" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="21"/>
-      <c r="C44" s="13"/>
+      <c r="B44" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" s="11">
+        <v>0</v>
+      </c>
       <c r="D44" s="2"/>
-      <c r="K44" s="37"/>
-      <c r="L44" s="38"/>
-      <c r="M44" s="43"/>
-      <c r="N44" s="20"/>
-      <c r="S44" s="36"/>
+      <c r="K44" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="L44" s="58"/>
+      <c r="M44" s="63">
+        <v>2</v>
+      </c>
+      <c r="N44" s="18"/>
+      <c r="S44" s="53"/>
     </row>
     <row r="45" spans="1:19" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H45" s="25" t="s">
+      <c r="H45" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="I45" s="26"/>
-      <c r="K45" s="39"/>
-      <c r="L45" s="40"/>
-      <c r="M45" s="44"/>
-      <c r="N45" s="20"/>
-      <c r="S45" s="36"/>
+      <c r="I45" s="51"/>
+      <c r="K45" s="59"/>
+      <c r="L45" s="60"/>
+      <c r="M45" s="64"/>
+      <c r="N45" s="18"/>
+      <c r="S45" s="53"/>
     </row>
     <row r="46" spans="1:19" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
-      <c r="K46" s="39"/>
-      <c r="L46" s="40"/>
-      <c r="M46" s="44"/>
-      <c r="N46" s="20"/>
-      <c r="S46" s="36"/>
+      <c r="H46" s="51"/>
+      <c r="I46" s="51"/>
+      <c r="K46" s="59"/>
+      <c r="L46" s="60"/>
+      <c r="M46" s="64"/>
+      <c r="N46" s="18"/>
+      <c r="S46" s="53"/>
     </row>
     <row r="47" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="13"/>
+      <c r="C47" s="11">
+        <v>2</v>
+      </c>
       <c r="D47" s="2"/>
-      <c r="K47" s="41"/>
-      <c r="L47" s="42"/>
-      <c r="M47" s="45"/>
-      <c r="N47" s="20"/>
-      <c r="S47" s="36"/>
+      <c r="K47" s="61"/>
+      <c r="L47" s="62"/>
+      <c r="M47" s="65"/>
+      <c r="N47" s="18"/>
+      <c r="S47" s="53"/>
     </row>
     <row r="48" spans="1:19" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="1"/>
       <c r="D48" s="4"/>
-      <c r="J48" s="27"/>
+      <c r="J48" s="52"/>
       <c r="L48" s="6">
         <v>3</v>
       </c>
-      <c r="S48" s="36"/>
+      <c r="S48" s="53"/>
     </row>
     <row r="49" spans="1:25" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="B49" s="25"/>
-      <c r="C49" s="25"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="14"/>
-      <c r="J49" s="27"/>
-      <c r="S49" s="36"/>
+      <c r="B49" s="50"/>
+      <c r="C49" s="50"/>
+      <c r="E49" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="F49" s="12">
+        <v>2</v>
+      </c>
+      <c r="J49" s="52"/>
+      <c r="S49" s="53"/>
     </row>
     <row r="50" spans="1:25" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="1"/>
@@ -2751,78 +2806,94 @@
       <c r="E50" s="6">
         <v>2</v>
       </c>
-      <c r="G50" s="36"/>
-      <c r="J50" s="27"/>
-      <c r="S50" s="36"/>
+      <c r="G50" s="53"/>
+      <c r="J50" s="52"/>
+      <c r="S50" s="53"/>
     </row>
     <row r="51" spans="1:25" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="22" t="s">
+      <c r="A51" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B51" s="21"/>
-      <c r="C51" s="13"/>
+      <c r="B51" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C51" s="11">
+        <v>1</v>
+      </c>
       <c r="D51" s="2"/>
-      <c r="G51" s="36"/>
-      <c r="J51" s="27"/>
-      <c r="S51" s="36"/>
+      <c r="G51" s="53"/>
+      <c r="J51" s="52"/>
+      <c r="S51" s="53"/>
     </row>
     <row r="52" spans="1:25" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E52" s="25" t="s">
+      <c r="E52" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="F52" s="26"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="15"/>
-      <c r="S52" s="36"/>
-      <c r="T52" s="103" t="s">
+      <c r="F52" s="51"/>
+      <c r="H52" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="I52" s="13">
+        <v>1</v>
+      </c>
+      <c r="S52" s="53"/>
+      <c r="T52" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="U52" s="103"/>
-      <c r="V52" s="103"/>
-      <c r="W52" s="103"/>
-      <c r="X52" s="103"/>
-      <c r="Y52" s="103"/>
+      <c r="U52" s="30"/>
+      <c r="V52" s="30"/>
+      <c r="W52" s="30"/>
+      <c r="X52" s="30"/>
+      <c r="Y52" s="30"/>
     </row>
     <row r="53" spans="1:25" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="22" t="s">
+      <c r="A53" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B53" s="21"/>
-      <c r="C53" s="13"/>
+      <c r="B53" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C53" s="11">
+        <v>1</v>
+      </c>
       <c r="D53" s="2"/>
-      <c r="G53" s="27"/>
+      <c r="G53" s="52"/>
       <c r="H53" s="7">
         <v>2</v>
       </c>
-      <c r="S53" s="36"/>
-      <c r="T53" s="103"/>
-      <c r="U53" s="103"/>
-      <c r="V53" s="103"/>
-      <c r="W53" s="103"/>
-      <c r="X53" s="103"/>
-      <c r="Y53" s="103"/>
+      <c r="S53" s="53"/>
+      <c r="T53" s="30"/>
+      <c r="U53" s="30"/>
+      <c r="V53" s="30"/>
+      <c r="W53" s="30"/>
+      <c r="X53" s="30"/>
+      <c r="Y53" s="30"/>
     </row>
     <row r="54" spans="1:25" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="1"/>
       <c r="D54" s="4"/>
-      <c r="G54" s="27"/>
-      <c r="S54" s="36"/>
-      <c r="T54" s="24"/>
-      <c r="U54" s="24"/>
-      <c r="V54" s="24"/>
-      <c r="W54" s="24"/>
-      <c r="X54" s="24"/>
-      <c r="Y54" s="24"/>
+      <c r="G54" s="52"/>
+      <c r="S54" s="53"/>
+      <c r="T54" s="22"/>
+      <c r="U54" s="22"/>
+      <c r="V54" s="22"/>
+      <c r="W54" s="22"/>
+      <c r="X54" s="22"/>
+      <c r="Y54" s="22"/>
     </row>
     <row r="55" spans="1:25" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="25"/>
-      <c r="C55" s="25"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="14"/>
-      <c r="S55" s="36"/>
+      <c r="B55" s="50"/>
+      <c r="C55" s="50"/>
+      <c r="E55" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="F55" s="12">
+        <v>2</v>
+      </c>
+      <c r="S55" s="53"/>
     </row>
     <row r="56" spans="1:25" ht="9.9499999999999993" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="1"/>
@@ -2830,78 +2901,93 @@
       <c r="E56" s="6">
         <v>2</v>
       </c>
-      <c r="T56" s="28"/>
-      <c r="U56" s="29"/>
-      <c r="V56" s="29"/>
-      <c r="W56" s="29"/>
-      <c r="X56" s="29"/>
-      <c r="Y56" s="30"/>
+      <c r="T56" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="U56" s="32"/>
+      <c r="V56" s="32"/>
+      <c r="W56" s="32"/>
+      <c r="X56" s="32"/>
+      <c r="Y56" s="33"/>
     </row>
     <row r="57" spans="1:25" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="22" t="s">
+      <c r="A57" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B57" s="21"/>
-      <c r="C57" s="13"/>
+      <c r="B57" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C57" s="11">
+        <v>0</v>
+      </c>
       <c r="D57" s="2"/>
-      <c r="T57" s="31"/>
-      <c r="U57" s="73"/>
-      <c r="V57" s="73"/>
-      <c r="W57" s="73"/>
-      <c r="X57" s="73"/>
-      <c r="Y57" s="32"/>
+      <c r="T57" s="34"/>
+      <c r="U57" s="35"/>
+      <c r="V57" s="35"/>
+      <c r="W57" s="35"/>
+      <c r="X57" s="35"/>
+      <c r="Y57" s="36"/>
     </row>
     <row r="58" spans="1:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="12"/>
+      <c r="A58" s="10"/>
       <c r="B58" s="9"/>
-      <c r="C58" s="12"/>
-      <c r="O58" s="65" t="s">
+      <c r="C58" s="10"/>
+      <c r="O58" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="P58" s="65"/>
-      <c r="Q58" s="65"/>
-      <c r="R58" s="65"/>
-      <c r="T58" s="31"/>
-      <c r="U58" s="73"/>
-      <c r="V58" s="73"/>
-      <c r="W58" s="73"/>
-      <c r="X58" s="73"/>
-      <c r="Y58" s="32"/>
+      <c r="P58" s="56"/>
+      <c r="Q58" s="56"/>
+      <c r="R58" s="56"/>
+      <c r="T58" s="34"/>
+      <c r="U58" s="35"/>
+      <c r="V58" s="35"/>
+      <c r="W58" s="35"/>
+      <c r="X58" s="35"/>
+      <c r="Y58" s="36"/>
     </row>
     <row r="59" spans="1:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="22" t="s">
+      <c r="A59" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B59" s="21" t="s">
+      <c r="B59" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C59" s="13"/>
-      <c r="T59" s="31"/>
-      <c r="U59" s="73"/>
-      <c r="V59" s="73"/>
-      <c r="W59" s="73"/>
-      <c r="X59" s="73"/>
-      <c r="Y59" s="32"/>
+      <c r="C59" s="11">
+        <v>2</v>
+      </c>
+      <c r="T59" s="34"/>
+      <c r="U59" s="35"/>
+      <c r="V59" s="35"/>
+      <c r="W59" s="35"/>
+      <c r="X59" s="35"/>
+      <c r="Y59" s="36"/>
     </row>
     <row r="60" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="1"/>
       <c r="D60" s="4"/>
-      <c r="T60" s="33"/>
-      <c r="U60" s="34"/>
-      <c r="V60" s="34"/>
-      <c r="W60" s="34"/>
-      <c r="X60" s="34"/>
-      <c r="Y60" s="35"/>
+      <c r="T60" s="37"/>
+      <c r="U60" s="38"/>
+      <c r="V60" s="38"/>
+      <c r="W60" s="38"/>
+      <c r="X60" s="38"/>
+      <c r="Y60" s="39"/>
     </row>
     <row r="61" spans="1:25" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="25" t="s">
+      <c r="A61" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="14"/>
-      <c r="S61" s="27"/>
+      <c r="B61" s="50"/>
+      <c r="C61" s="50"/>
+      <c r="E61" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F61" s="12">
+        <v>1</v>
+      </c>
+      <c r="S61" s="52"/>
+      <c r="X61" s="6">
+        <v>8</v>
+      </c>
     </row>
     <row r="62" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="1"/>
@@ -2909,62 +2995,76 @@
       <c r="E62" s="6">
         <v>2</v>
       </c>
-      <c r="G62" s="36"/>
-      <c r="S62" s="27"/>
+      <c r="G62" s="53"/>
+      <c r="S62" s="52"/>
     </row>
     <row r="63" spans="1:25" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="22" t="s">
+      <c r="A63" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B63" s="21"/>
-      <c r="C63" s="13"/>
+      <c r="B63" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C63" s="11">
+        <v>2</v>
+      </c>
       <c r="D63" s="2"/>
-      <c r="G63" s="36"/>
-      <c r="S63" s="27"/>
+      <c r="G63" s="53"/>
+      <c r="S63" s="52"/>
     </row>
     <row r="64" spans="1:25" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E64" s="25" t="s">
+      <c r="E64" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="F64" s="25"/>
-      <c r="H64" s="11"/>
-      <c r="I64" s="15"/>
-      <c r="S64" s="27"/>
+      <c r="F64" s="50"/>
+      <c r="H64" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="I64" s="13">
+        <v>1</v>
+      </c>
+      <c r="S64" s="52"/>
     </row>
     <row r="65" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="22" t="s">
+      <c r="A65" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B65" s="21" t="s">
+      <c r="B65" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="C65" s="13"/>
+      <c r="C65" s="11">
+        <v>1</v>
+      </c>
       <c r="D65" s="2"/>
       <c r="E65" s="5"/>
-      <c r="G65" s="27"/>
+      <c r="G65" s="52"/>
       <c r="H65" s="7">
         <v>2</v>
       </c>
-      <c r="J65" s="36"/>
-      <c r="S65" s="27"/>
+      <c r="J65" s="53"/>
+      <c r="S65" s="52"/>
     </row>
     <row r="66" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="1"/>
       <c r="D66" s="4"/>
-      <c r="G66" s="27"/>
-      <c r="J66" s="36"/>
-      <c r="S66" s="27"/>
+      <c r="G66" s="52"/>
+      <c r="J66" s="53"/>
+      <c r="S66" s="52"/>
     </row>
     <row r="67" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="25" t="s">
+      <c r="A67" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="B67" s="25"/>
-      <c r="C67" s="25"/>
-      <c r="E67" s="10"/>
-      <c r="F67" s="14"/>
-      <c r="J67" s="36"/>
-      <c r="S67" s="27"/>
+      <c r="B67" s="50"/>
+      <c r="C67" s="50"/>
+      <c r="E67" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F67" s="12">
+        <v>2</v>
+      </c>
+      <c r="J67" s="53"/>
+      <c r="S67" s="52"/>
     </row>
     <row r="68" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B68" s="1"/>
@@ -2972,83 +3072,96 @@
       <c r="E68" s="6">
         <v>2</v>
       </c>
-      <c r="J68" s="36"/>
-      <c r="S68" s="27"/>
+      <c r="J68" s="53"/>
+      <c r="S68" s="52"/>
     </row>
     <row r="69" spans="1:19" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="22" t="s">
+      <c r="A69" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B69" s="21"/>
-      <c r="C69" s="13"/>
+      <c r="B69" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C69" s="11">
+        <v>3</v>
+      </c>
       <c r="D69" s="2"/>
-      <c r="K69" s="48"/>
-      <c r="L69" s="49"/>
-      <c r="M69" s="54"/>
-      <c r="N69" s="18"/>
-      <c r="S69" s="27"/>
-    </row>
-    <row r="70" spans="1:19" s="76" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="22"/>
-      <c r="B70" s="98"/>
-      <c r="C70" s="98"/>
-      <c r="D70" s="99"/>
-      <c r="H70" s="25" t="s">
+      <c r="K69" s="74" t="s">
+        <v>99</v>
+      </c>
+      <c r="L69" s="75"/>
+      <c r="M69" s="71">
+        <v>1</v>
+      </c>
+      <c r="N69" s="16"/>
+      <c r="S69" s="52"/>
+    </row>
+    <row r="70" spans="1:19" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="20"/>
+      <c r="B70" s="10"/>
+      <c r="C70" s="10"/>
+      <c r="H70" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="I70" s="25"/>
-      <c r="K70" s="50"/>
-      <c r="L70" s="100"/>
-      <c r="M70" s="55"/>
-      <c r="N70" s="80"/>
-      <c r="S70" s="27"/>
+      <c r="I70" s="50"/>
+      <c r="K70" s="76"/>
+      <c r="L70" s="77"/>
+      <c r="M70" s="72"/>
+      <c r="N70" s="16"/>
+      <c r="S70" s="52"/>
     </row>
     <row r="71" spans="1:19" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G71" s="97"/>
-      <c r="H71" s="25"/>
-      <c r="I71" s="25"/>
-      <c r="K71" s="50"/>
-      <c r="L71" s="51"/>
-      <c r="M71" s="55"/>
-      <c r="N71" s="18"/>
-      <c r="S71" s="27"/>
+      <c r="G71" s="26"/>
+      <c r="H71" s="50"/>
+      <c r="I71" s="50"/>
+      <c r="K71" s="76"/>
+      <c r="L71" s="77"/>
+      <c r="M71" s="72"/>
+      <c r="N71" s="16"/>
+      <c r="S71" s="52"/>
     </row>
     <row r="72" spans="1:19" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="22" t="s">
+      <c r="A72" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="95" t="s">
+      <c r="B72" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C72" s="13"/>
+      <c r="C72" s="11">
+        <v>2</v>
+      </c>
       <c r="D72" s="2"/>
-      <c r="K72" s="52"/>
-      <c r="L72" s="53"/>
-      <c r="M72" s="56"/>
-      <c r="N72" s="18"/>
-      <c r="S72" s="27"/>
+      <c r="K72" s="78"/>
+      <c r="L72" s="79"/>
+      <c r="M72" s="73"/>
+      <c r="N72" s="16"/>
+      <c r="S72" s="52"/>
     </row>
     <row r="73" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B73" s="1"/>
       <c r="D73" s="4"/>
-      <c r="J73" s="27"/>
+      <c r="J73" s="52"/>
       <c r="L73" s="6">
         <v>3</v>
       </c>
-      <c r="N73" s="36"/>
-      <c r="S73" s="27"/>
+      <c r="N73" s="53"/>
+      <c r="S73" s="52"/>
     </row>
     <row r="74" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="25" t="s">
+      <c r="A74" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="B74" s="25"/>
-      <c r="C74" s="25"/>
-      <c r="E74" s="10"/>
-      <c r="F74" s="14"/>
-      <c r="J74" s="27"/>
-      <c r="N74" s="36"/>
-      <c r="S74" s="27"/>
+      <c r="B74" s="50"/>
+      <c r="C74" s="50"/>
+      <c r="E74" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F74" s="12">
+        <v>1</v>
+      </c>
+      <c r="J74" s="52"/>
+      <c r="N74" s="53"/>
+      <c r="S74" s="52"/>
     </row>
     <row r="75" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1"/>
@@ -3056,67 +3169,83 @@
       <c r="E75" s="6">
         <v>2</v>
       </c>
-      <c r="G75" s="36"/>
-      <c r="J75" s="27"/>
-      <c r="N75" s="36"/>
-      <c r="S75" s="27"/>
+      <c r="G75" s="53"/>
+      <c r="J75" s="52"/>
+      <c r="N75" s="53"/>
+      <c r="S75" s="52"/>
     </row>
     <row r="76" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="22" t="s">
+      <c r="A76" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B76" s="21"/>
-      <c r="C76" s="13"/>
+      <c r="B76" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C76" s="11">
+        <v>1</v>
+      </c>
       <c r="D76" s="2"/>
-      <c r="G76" s="36"/>
-      <c r="J76" s="27"/>
-      <c r="N76" s="36"/>
-      <c r="S76" s="27"/>
+      <c r="G76" s="53"/>
+      <c r="J76" s="52"/>
+      <c r="N76" s="53"/>
+      <c r="S76" s="52"/>
     </row>
     <row r="77" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E77" s="25" t="s">
+      <c r="E77" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="F77" s="25"/>
-      <c r="H77" s="11"/>
-      <c r="I77" s="15"/>
-      <c r="N77" s="36"/>
-      <c r="S77" s="27"/>
+      <c r="F77" s="50"/>
+      <c r="H77" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I77" s="13">
+        <v>2</v>
+      </c>
+      <c r="N77" s="53"/>
+      <c r="S77" s="52"/>
     </row>
     <row r="78" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="22" t="s">
+      <c r="A78" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B78" s="21"/>
-      <c r="C78" s="13"/>
+      <c r="B78" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C78" s="11">
+        <v>2</v>
+      </c>
       <c r="D78" s="2"/>
-      <c r="G78" s="27"/>
+      <c r="G78" s="52"/>
       <c r="H78" s="6">
         <v>2</v>
       </c>
-      <c r="N78" s="36"/>
-      <c r="S78" s="27"/>
+      <c r="N78" s="53"/>
+      <c r="S78" s="52"/>
     </row>
     <row r="79" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="1"/>
       <c r="D79" s="4"/>
-      <c r="G79" s="27"/>
-      <c r="N79" s="36"/>
-      <c r="S79" s="27"/>
+      <c r="G79" s="52"/>
+      <c r="N79" s="53"/>
+      <c r="S79" s="52"/>
     </row>
     <row r="80" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="25" t="s">
+      <c r="A80" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="14"/>
-      <c r="N80" s="36"/>
-      <c r="O80" s="74"/>
-      <c r="P80" s="74"/>
-      <c r="Q80" s="74"/>
-      <c r="S80" s="27"/>
+      <c r="B80" s="50"/>
+      <c r="C80" s="50"/>
+      <c r="E80" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="F80" s="12">
+        <v>3</v>
+      </c>
+      <c r="N80" s="53"/>
+      <c r="O80" s="23"/>
+      <c r="P80" s="23"/>
+      <c r="Q80" s="23"/>
+      <c r="S80" s="52"/>
     </row>
     <row r="81" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="1"/>
@@ -3124,63 +3253,77 @@
       <c r="E81" s="6">
         <v>2</v>
       </c>
-      <c r="N81" s="36"/>
-      <c r="S81" s="27"/>
+      <c r="N81" s="53"/>
+      <c r="S81" s="52"/>
     </row>
     <row r="82" spans="1:19" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="22" t="s">
+      <c r="A82" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B82" s="21"/>
-      <c r="C82" s="13"/>
+      <c r="B82" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C82" s="11">
+        <v>0</v>
+      </c>
       <c r="D82" s="2"/>
-      <c r="O82" s="67"/>
+      <c r="O82" s="67" t="s">
+        <v>46</v>
+      </c>
       <c r="P82" s="67"/>
       <c r="Q82" s="67"/>
-      <c r="R82" s="68"/>
+      <c r="R82" s="27">
+        <v>1</v>
+      </c>
     </row>
     <row r="83" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K83" s="102" t="s">
+      <c r="K83" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="L83" s="102"/>
-      <c r="M83" s="102"/>
-      <c r="N83" s="19"/>
-      <c r="O83" s="69"/>
-      <c r="P83" s="69"/>
-      <c r="Q83" s="69"/>
-      <c r="R83" s="70"/>
+      <c r="L83" s="70"/>
+      <c r="M83" s="70"/>
+      <c r="N83" s="17"/>
+      <c r="O83" s="68"/>
+      <c r="P83" s="68"/>
+      <c r="Q83" s="68"/>
+      <c r="R83" s="28"/>
     </row>
     <row r="84" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="22" t="s">
+      <c r="A84" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B84" s="13" t="s">
+      <c r="B84" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C84" s="13"/>
-      <c r="O84" s="71"/>
-      <c r="P84" s="71"/>
-      <c r="Q84" s="71"/>
-      <c r="R84" s="72"/>
+      <c r="C84" s="11">
+        <v>3</v>
+      </c>
+      <c r="O84" s="69"/>
+      <c r="P84" s="69"/>
+      <c r="Q84" s="69"/>
+      <c r="R84" s="29"/>
     </row>
     <row r="85" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B85" s="1"/>
       <c r="D85" s="4"/>
-      <c r="N85" s="47"/>
+      <c r="N85" s="40"/>
       <c r="Q85" s="6">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="25" t="s">
+      <c r="A86" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="B86" s="25"/>
-      <c r="C86" s="25"/>
-      <c r="E86" s="10"/>
-      <c r="F86" s="14"/>
-      <c r="N86" s="47"/>
+      <c r="B86" s="50"/>
+      <c r="C86" s="50"/>
+      <c r="E86" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F86" s="12">
+        <v>2</v>
+      </c>
+      <c r="N86" s="40"/>
     </row>
     <row r="87" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B87" s="1"/>
@@ -3188,63 +3331,79 @@
       <c r="E87" s="6">
         <v>2</v>
       </c>
-      <c r="G87" s="36"/>
-      <c r="N87" s="47"/>
+      <c r="G87" s="53"/>
+      <c r="N87" s="40"/>
     </row>
     <row r="88" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="22" t="s">
+      <c r="A88" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="B88" s="23"/>
-      <c r="C88" s="13"/>
+      <c r="B88" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C88" s="11">
+        <v>0</v>
+      </c>
       <c r="D88" s="2"/>
-      <c r="G88" s="36"/>
-      <c r="N88" s="47"/>
+      <c r="G88" s="53"/>
+      <c r="N88" s="40"/>
     </row>
     <row r="89" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="8"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
-      <c r="E89" s="25" t="s">
+      <c r="E89" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="F89" s="26"/>
-      <c r="H89" s="11"/>
-      <c r="I89" s="15"/>
-      <c r="N89" s="47"/>
+      <c r="F89" s="51"/>
+      <c r="H89" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I89" s="13">
+        <v>2</v>
+      </c>
+      <c r="N89" s="40"/>
     </row>
     <row r="90" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="22" t="s">
+      <c r="A90" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B90" s="21"/>
-      <c r="C90" s="13"/>
+      <c r="B90" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C90" s="11">
+        <v>1</v>
+      </c>
       <c r="D90" s="2"/>
       <c r="E90" s="5"/>
-      <c r="G90" s="27"/>
+      <c r="G90" s="52"/>
       <c r="H90" s="7">
         <v>2</v>
       </c>
-      <c r="J90" s="36"/>
-      <c r="N90" s="47"/>
+      <c r="J90" s="53"/>
+      <c r="N90" s="40"/>
     </row>
     <row r="91" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B91" s="1"/>
       <c r="D91" s="4"/>
-      <c r="G91" s="27"/>
-      <c r="J91" s="36"/>
-      <c r="N91" s="47"/>
+      <c r="G91" s="52"/>
+      <c r="J91" s="53"/>
+      <c r="N91" s="40"/>
     </row>
     <row r="92" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="25" t="s">
+      <c r="A92" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="B92" s="26"/>
-      <c r="C92" s="26"/>
-      <c r="E92" s="10"/>
-      <c r="F92" s="14"/>
-      <c r="J92" s="36"/>
-      <c r="N92" s="47"/>
+      <c r="B92" s="51"/>
+      <c r="C92" s="51"/>
+      <c r="E92" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="F92" s="12">
+        <v>0</v>
+      </c>
+      <c r="J92" s="53"/>
+      <c r="N92" s="40"/>
     </row>
     <row r="93" spans="1:19" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B93" s="1"/>
@@ -3252,74 +3411,87 @@
       <c r="E93" s="6">
         <v>2</v>
       </c>
-      <c r="J93" s="36"/>
-      <c r="N93" s="47"/>
+      <c r="J93" s="53"/>
+      <c r="N93" s="40"/>
     </row>
     <row r="94" spans="1:19" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="22" t="s">
+      <c r="A94" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B94" s="21"/>
-      <c r="C94" s="13"/>
+      <c r="B94" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C94" s="11">
+        <v>0</v>
+      </c>
       <c r="D94" s="2"/>
-      <c r="K94" s="37"/>
-      <c r="L94" s="38"/>
-      <c r="M94" s="43"/>
-      <c r="N94" s="20"/>
-    </row>
-    <row r="95" spans="1:19" s="76" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="22"/>
-      <c r="B95" s="98"/>
-      <c r="C95" s="98"/>
-      <c r="D95" s="99"/>
-      <c r="H95" s="25" t="s">
+      <c r="K94" s="57" t="s">
+        <v>46</v>
+      </c>
+      <c r="L94" s="58"/>
+      <c r="M94" s="63">
+        <v>2</v>
+      </c>
+      <c r="N94" s="18"/>
+    </row>
+    <row r="95" spans="1:19" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="20"/>
+      <c r="B95" s="10"/>
+      <c r="C95" s="10"/>
+      <c r="H95" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="I95" s="25"/>
-      <c r="K95" s="39"/>
-      <c r="L95" s="101"/>
-      <c r="M95" s="44"/>
-      <c r="N95" s="81"/>
+      <c r="I95" s="50"/>
+      <c r="K95" s="59"/>
+      <c r="L95" s="60"/>
+      <c r="M95" s="64"/>
+      <c r="N95" s="18"/>
     </row>
     <row r="96" spans="1:19" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H96" s="25"/>
-      <c r="I96" s="25"/>
-      <c r="K96" s="39"/>
-      <c r="L96" s="40"/>
-      <c r="M96" s="44"/>
-      <c r="N96" s="20"/>
+      <c r="H96" s="50"/>
+      <c r="I96" s="50"/>
+      <c r="K96" s="59"/>
+      <c r="L96" s="60"/>
+      <c r="M96" s="64"/>
+      <c r="N96" s="18"/>
     </row>
     <row r="97" spans="1:17" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="22" t="s">
+      <c r="A97" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B97" s="21" t="s">
+      <c r="B97" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C97" s="13"/>
+      <c r="C97" s="11">
+        <v>2</v>
+      </c>
       <c r="D97" s="2"/>
-      <c r="K97" s="41"/>
-      <c r="L97" s="42"/>
-      <c r="M97" s="45"/>
-      <c r="N97" s="20"/>
+      <c r="K97" s="61"/>
+      <c r="L97" s="62"/>
+      <c r="M97" s="65"/>
+      <c r="N97" s="18"/>
     </row>
     <row r="98" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B98" s="1"/>
       <c r="D98" s="4"/>
-      <c r="J98" s="27"/>
+      <c r="J98" s="52"/>
       <c r="L98" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:17" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="25" t="s">
+      <c r="A99" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="B99" s="25"/>
-      <c r="C99" s="25"/>
-      <c r="E99" s="10"/>
-      <c r="F99" s="14"/>
-      <c r="J99" s="27"/>
+      <c r="B99" s="50"/>
+      <c r="C99" s="50"/>
+      <c r="E99" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F99" s="12">
+        <v>0</v>
+      </c>
+      <c r="J99" s="52"/>
     </row>
     <row r="100" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B100" s="1"/>
@@ -3327,35 +3499,47 @@
       <c r="E100" s="6">
         <v>2</v>
       </c>
-      <c r="G100" s="36"/>
-      <c r="J100" s="27"/>
+      <c r="G100" s="53"/>
+      <c r="J100" s="52"/>
     </row>
     <row r="101" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="22" t="s">
+      <c r="A101" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B101" s="21"/>
-      <c r="C101" s="13"/>
+      <c r="B101" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C101" s="11">
+        <v>1</v>
+      </c>
       <c r="D101" s="2"/>
-      <c r="G101" s="36"/>
-      <c r="J101" s="27"/>
+      <c r="G101" s="53"/>
+      <c r="J101" s="52"/>
     </row>
     <row r="102" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E102" s="25" t="s">
+      <c r="E102" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="F102" s="26"/>
-      <c r="H102" s="11"/>
-      <c r="I102" s="15"/>
+      <c r="F102" s="51"/>
+      <c r="H102" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="I102" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="103" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="22" t="s">
+      <c r="A103" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B103" s="21"/>
-      <c r="C103" s="13"/>
+      <c r="B103" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C103" s="11">
+        <v>2</v>
+      </c>
       <c r="D103" s="2"/>
-      <c r="G103" s="27"/>
+      <c r="G103" s="52"/>
       <c r="H103" s="7">
         <v>2</v>
       </c>
@@ -3363,16 +3547,20 @@
     <row r="104" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B104" s="1"/>
       <c r="D104" s="4"/>
-      <c r="G104" s="27"/>
+      <c r="G104" s="52"/>
     </row>
     <row r="105" spans="1:17" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="25" t="s">
+      <c r="A105" s="50" t="s">
         <v>62</v>
       </c>
-      <c r="B105" s="25"/>
-      <c r="C105" s="25"/>
-      <c r="E105" s="10"/>
-      <c r="F105" s="14"/>
+      <c r="B105" s="50"/>
+      <c r="C105" s="50"/>
+      <c r="E105" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="F105" s="12">
+        <v>1</v>
+      </c>
     </row>
     <row r="106" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B106" s="1"/>
@@ -3382,141 +3570,178 @@
       </c>
     </row>
     <row r="107" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="22" t="s">
+      <c r="A107" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B107" s="21"/>
-      <c r="C107" s="13"/>
+      <c r="B107" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C107" s="11">
+        <v>0</v>
+      </c>
       <c r="D107" s="2"/>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B110" s="64" t="s">
+      <c r="B110" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="64"/>
-      <c r="D110" s="64"/>
-      <c r="E110" s="64"/>
-      <c r="F110" s="64"/>
-      <c r="G110" s="64"/>
-      <c r="H110" s="64"/>
-      <c r="I110" s="64"/>
-      <c r="J110" s="64"/>
-      <c r="K110" s="64"/>
-      <c r="L110" s="64"/>
-      <c r="M110" s="64"/>
-      <c r="N110" s="64"/>
-      <c r="O110" s="64"/>
-      <c r="P110" s="64"/>
-      <c r="Q110" s="64"/>
+      <c r="C110" s="55"/>
+      <c r="D110" s="55"/>
+      <c r="E110" s="55"/>
+      <c r="F110" s="55"/>
+      <c r="G110" s="55"/>
+      <c r="H110" s="55"/>
+      <c r="I110" s="55"/>
+      <c r="J110" s="55"/>
+      <c r="K110" s="55"/>
+      <c r="L110" s="55"/>
+      <c r="M110" s="55"/>
+      <c r="N110" s="55"/>
+      <c r="O110" s="55"/>
+      <c r="P110" s="55"/>
+      <c r="Q110" s="55"/>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B111" s="64" t="s">
+      <c r="B111" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="C111" s="64"/>
-      <c r="D111" s="64"/>
-      <c r="E111" s="64"/>
-      <c r="F111" s="64"/>
-      <c r="G111" s="64"/>
-      <c r="H111" s="64"/>
-      <c r="I111" s="64"/>
-      <c r="J111" s="64"/>
-      <c r="K111" s="64"/>
-      <c r="L111" s="64"/>
-      <c r="M111" s="64"/>
-      <c r="N111" s="64"/>
-      <c r="O111" s="64"/>
-      <c r="P111" s="64"/>
-      <c r="Q111" s="64"/>
+      <c r="C111" s="55"/>
+      <c r="D111" s="55"/>
+      <c r="E111" s="55"/>
+      <c r="F111" s="55"/>
+      <c r="G111" s="55"/>
+      <c r="H111" s="55"/>
+      <c r="I111" s="55"/>
+      <c r="J111" s="55"/>
+      <c r="K111" s="55"/>
+      <c r="L111" s="55"/>
+      <c r="M111" s="55"/>
+      <c r="N111" s="55"/>
+      <c r="O111" s="55"/>
+      <c r="P111" s="55"/>
+      <c r="Q111" s="55"/>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B112" s="63" t="s">
+      <c r="B112" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="C112" s="63"/>
-      <c r="D112" s="63"/>
-      <c r="E112" s="63"/>
-      <c r="F112" s="63"/>
-      <c r="G112" s="63"/>
-      <c r="H112" s="63"/>
-      <c r="I112" s="63"/>
-      <c r="J112" s="63"/>
-      <c r="K112" s="63"/>
-      <c r="L112" s="63"/>
-      <c r="M112" s="63"/>
-      <c r="N112" s="63"/>
-      <c r="O112" s="63"/>
-      <c r="P112" s="63"/>
-      <c r="Q112" s="63"/>
+      <c r="C112" s="54"/>
+      <c r="D112" s="54"/>
+      <c r="E112" s="54"/>
+      <c r="F112" s="54"/>
+      <c r="G112" s="54"/>
+      <c r="H112" s="54"/>
+      <c r="I112" s="54"/>
+      <c r="J112" s="54"/>
+      <c r="K112" s="54"/>
+      <c r="L112" s="54"/>
+      <c r="M112" s="54"/>
+      <c r="N112" s="54"/>
+      <c r="O112" s="54"/>
+      <c r="P112" s="54"/>
+      <c r="Q112" s="54"/>
     </row>
     <row r="113" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B113" s="63" t="s">
+      <c r="B113" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="C113" s="63"/>
-      <c r="D113" s="63"/>
-      <c r="E113" s="63"/>
-      <c r="F113" s="63"/>
-      <c r="G113" s="63"/>
-      <c r="H113" s="63"/>
-      <c r="I113" s="63"/>
-      <c r="J113" s="63"/>
-      <c r="K113" s="63"/>
-      <c r="L113" s="63"/>
-      <c r="M113" s="63"/>
-      <c r="N113" s="63"/>
-      <c r="O113" s="63"/>
-      <c r="P113" s="63"/>
-      <c r="Q113" s="63"/>
+      <c r="C113" s="54"/>
+      <c r="D113" s="54"/>
+      <c r="E113" s="54"/>
+      <c r="F113" s="54"/>
+      <c r="G113" s="54"/>
+      <c r="H113" s="54"/>
+      <c r="I113" s="54"/>
+      <c r="J113" s="54"/>
+      <c r="K113" s="54"/>
+      <c r="L113" s="54"/>
+      <c r="M113" s="54"/>
+      <c r="N113" s="54"/>
+      <c r="O113" s="54"/>
+      <c r="P113" s="54"/>
+      <c r="Q113" s="54"/>
     </row>
     <row r="114" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B114" s="63" t="s">
+      <c r="B114" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="C114" s="63"/>
-      <c r="D114" s="63"/>
-      <c r="E114" s="63"/>
-      <c r="F114" s="63"/>
-      <c r="G114" s="63"/>
-      <c r="H114" s="63"/>
-      <c r="I114" s="63"/>
-      <c r="J114" s="63"/>
-      <c r="K114" s="63"/>
-      <c r="L114" s="63"/>
-      <c r="M114" s="63"/>
-      <c r="N114" s="63"/>
-      <c r="O114" s="63"/>
-      <c r="P114" s="63"/>
-      <c r="Q114" s="63"/>
+      <c r="C114" s="54"/>
+      <c r="D114" s="54"/>
+      <c r="E114" s="54"/>
+      <c r="F114" s="54"/>
+      <c r="G114" s="54"/>
+      <c r="H114" s="54"/>
+      <c r="I114" s="54"/>
+      <c r="J114" s="54"/>
+      <c r="K114" s="54"/>
+      <c r="L114" s="54"/>
+      <c r="M114" s="54"/>
+      <c r="N114" s="54"/>
+      <c r="O114" s="54"/>
+      <c r="P114" s="54"/>
+      <c r="Q114" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="98">
-    <mergeCell ref="H70:I71"/>
-    <mergeCell ref="H95:I96"/>
-    <mergeCell ref="O58:R58"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="G103:G104"/>
+    <mergeCell ref="A105:C105"/>
+    <mergeCell ref="S35:S55"/>
+    <mergeCell ref="S61:S81"/>
+    <mergeCell ref="K94:L97"/>
+    <mergeCell ref="M94:M97"/>
+    <mergeCell ref="J98:J101"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="O82:Q84"/>
+    <mergeCell ref="K83:M83"/>
+    <mergeCell ref="N85:N93"/>
+    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="J90:J93"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="K69:L72"/>
+    <mergeCell ref="M69:M72"/>
+    <mergeCell ref="J73:J76"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:Y3"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="O7:R7"/>
     <mergeCell ref="T7:V7"/>
-    <mergeCell ref="U21:V22"/>
-    <mergeCell ref="U19:V20"/>
-    <mergeCell ref="T12:U13"/>
-    <mergeCell ref="V12:V13"/>
-    <mergeCell ref="T15:U16"/>
-    <mergeCell ref="V15:V16"/>
-    <mergeCell ref="T14:V14"/>
-    <mergeCell ref="R32:R34"/>
-    <mergeCell ref="R82:R84"/>
-    <mergeCell ref="T52:Y53"/>
-    <mergeCell ref="T56:Y60"/>
-    <mergeCell ref="N35:N43"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O32:Q34"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="G20:I21"/>
+    <mergeCell ref="N23:N31"/>
+    <mergeCell ref="K33:M33"/>
+    <mergeCell ref="M19:M22"/>
+    <mergeCell ref="K19:L22"/>
+    <mergeCell ref="K44:L47"/>
+    <mergeCell ref="M44:M47"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="J15:J18"/>
+    <mergeCell ref="J23:J26"/>
+    <mergeCell ref="J40:J43"/>
+    <mergeCell ref="J48:J51"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H45:I46"/>
+    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="G37:G38"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="H45:I46"/>
-    <mergeCell ref="A30:C30"/>
     <mergeCell ref="B114:Q114"/>
     <mergeCell ref="E52:F52"/>
     <mergeCell ref="G53:G54"/>
@@ -3531,64 +3756,31 @@
     <mergeCell ref="E64:F64"/>
     <mergeCell ref="G65:G66"/>
     <mergeCell ref="J65:J68"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="J15:J18"/>
-    <mergeCell ref="J23:J26"/>
-    <mergeCell ref="J40:J43"/>
-    <mergeCell ref="J48:J51"/>
-    <mergeCell ref="K33:M33"/>
-    <mergeCell ref="M19:M22"/>
-    <mergeCell ref="K19:L22"/>
-    <mergeCell ref="K44:L47"/>
-    <mergeCell ref="M44:M47"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O32:Q34"/>
-    <mergeCell ref="G28:G29"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="G20:I21"/>
-    <mergeCell ref="N23:N31"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:Y3"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="K69:L72"/>
-    <mergeCell ref="M69:M72"/>
-    <mergeCell ref="J73:J76"/>
+    <mergeCell ref="O58:R58"/>
     <mergeCell ref="N73:N81"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="H70:I71"/>
+    <mergeCell ref="H95:I96"/>
     <mergeCell ref="A74:C74"/>
     <mergeCell ref="G75:G76"/>
     <mergeCell ref="E77:F77"/>
     <mergeCell ref="G78:G79"/>
     <mergeCell ref="A80:C80"/>
-    <mergeCell ref="N85:N93"/>
-    <mergeCell ref="A86:C86"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="E89:F89"/>
     <mergeCell ref="G90:G91"/>
-    <mergeCell ref="J90:J93"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="G103:G104"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="S35:S55"/>
-    <mergeCell ref="S61:S81"/>
-    <mergeCell ref="K94:L97"/>
-    <mergeCell ref="M94:M97"/>
-    <mergeCell ref="J98:J101"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="G100:G101"/>
-    <mergeCell ref="O82:Q84"/>
-    <mergeCell ref="K83:M83"/>
+    <mergeCell ref="U21:V22"/>
+    <mergeCell ref="U19:V20"/>
+    <mergeCell ref="T12:U13"/>
+    <mergeCell ref="V12:V13"/>
+    <mergeCell ref="T15:U16"/>
+    <mergeCell ref="V15:V16"/>
+    <mergeCell ref="T14:V14"/>
+    <mergeCell ref="R32:R34"/>
+    <mergeCell ref="R82:R84"/>
+    <mergeCell ref="T52:Y53"/>
+    <mergeCell ref="T56:Y60"/>
+    <mergeCell ref="N35:N43"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>

--- a/IzlocilniBoji/SP 2026 - izlocilni.xlsx
+++ b/IzlocilniBoji/SP 2026 - izlocilni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rihar\Documents\SP2026\IzlocilniBoji\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41E3802-E688-4F52-A939-A34217344E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A87845A-6FD8-4CB1-AD5A-1E182BCD5811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="zakljucni boji" sheetId="4" r:id="rId1"/>
@@ -798,7 +798,7 @@
     <t>GANA</t>
   </si>
   <si>
-    <t>Boštjan Prevc</t>
+    <t>Matej Pintar</t>
   </si>
 </sst>
 </file>
@@ -2271,11 +2271,11 @@
       </c>
       <c r="G12" s="53"/>
       <c r="T12" s="41" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="U12" s="42"/>
       <c r="V12" s="47">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2286,7 +2286,7 @@
         <v>85</v>
       </c>
       <c r="C13" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2"/>
       <c r="G13" s="53"/>
@@ -2329,11 +2329,11 @@
       </c>
       <c r="J15" s="53"/>
       <c r="T15" s="41" t="s">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="U15" s="42"/>
       <c r="V15" s="47">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2355,7 +2355,7 @@
         <v>86</v>
       </c>
       <c r="F17" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="53"/>
       <c r="U17" s="7">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="L19" s="75"/>
       <c r="M19" s="71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19" s="16"/>
       <c r="U19" s="45" t="s">
@@ -2416,7 +2416,7 @@
       <c r="M21" s="72"/>
       <c r="N21" s="16"/>
       <c r="U21" s="41" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="V21" s="42"/>
     </row>
@@ -2428,7 +2428,7 @@
         <v>33</v>
       </c>
       <c r="C22" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2"/>
       <c r="K22" s="78"/>
@@ -2483,7 +2483,7 @@
         <v>34</v>
       </c>
       <c r="C26" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2"/>
       <c r="G26" s="53"/>
@@ -2511,7 +2511,7 @@
         <v>82</v>
       </c>
       <c r="C28" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="2"/>
       <c r="G28" s="52"/>
@@ -2559,16 +2559,16 @@
         <v>35</v>
       </c>
       <c r="C32" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="2"/>
       <c r="O32" s="67" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="P32" s="67"/>
       <c r="Q32" s="67"/>
       <c r="R32" s="27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2591,7 +2591,7 @@
         <v>94</v>
       </c>
       <c r="C34" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O34" s="69"/>
       <c r="P34" s="69"/>
@@ -2617,7 +2617,7 @@
         <v>94</v>
       </c>
       <c r="F36" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N36" s="40"/>
       <c r="S36" s="53"/>
@@ -2640,7 +2640,7 @@
         <v>95</v>
       </c>
       <c r="C38" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2"/>
       <c r="G38" s="53"/>
@@ -2655,11 +2655,11 @@
         <v>67</v>
       </c>
       <c r="F39" s="51"/>
-      <c r="H39" s="19" t="s">
-        <v>88</v>
+      <c r="H39" s="21" t="s">
+        <v>94</v>
       </c>
       <c r="I39" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N39" s="40"/>
       <c r="S39" s="53"/>
@@ -2672,7 +2672,7 @@
         <v>88</v>
       </c>
       <c r="C40" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="5"/>
@@ -2726,15 +2726,15 @@
         <v>96</v>
       </c>
       <c r="C44" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" s="2"/>
       <c r="K44" s="57" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="L44" s="58"/>
       <c r="M44" s="63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N44" s="18"/>
       <c r="S44" s="53"/>
@@ -2795,7 +2795,7 @@
         <v>41</v>
       </c>
       <c r="F49" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J49" s="52"/>
       <c r="S49" s="53"/>
@@ -2888,10 +2888,10 @@
       <c r="B55" s="50"/>
       <c r="C55" s="50"/>
       <c r="E55" s="19" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F55" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S55" s="53"/>
     </row>
@@ -2902,7 +2902,7 @@
         <v>2</v>
       </c>
       <c r="T56" s="31" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="U56" s="32"/>
       <c r="V56" s="32"/>
@@ -2918,7 +2918,7 @@
         <v>97</v>
       </c>
       <c r="C57" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D57" s="2"/>
       <c r="T57" s="34"/>
@@ -2953,7 +2953,7 @@
         <v>43</v>
       </c>
       <c r="C59" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T59" s="34"/>
       <c r="U59" s="35"/>
@@ -2982,7 +2982,7 @@
         <v>43</v>
       </c>
       <c r="F61" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S61" s="52"/>
       <c r="X61" s="6">
@@ -3006,7 +3006,7 @@
         <v>83</v>
       </c>
       <c r="C63" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" s="2"/>
       <c r="G63" s="53"/>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F64" s="50"/>
       <c r="H64" s="19" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="I64" s="13">
         <v>1</v>
@@ -3061,7 +3061,7 @@
         <v>91</v>
       </c>
       <c r="F67" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J67" s="53"/>
       <c r="S67" s="52"/>
@@ -3083,7 +3083,7 @@
         <v>91</v>
       </c>
       <c r="C69" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69" s="2"/>
       <c r="K69" s="74" t="s">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="L69" s="75"/>
       <c r="M69" s="71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N69" s="16"/>
       <c r="S69" s="52"/>
@@ -3157,7 +3157,7 @@
         <v>45</v>
       </c>
       <c r="F74" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" s="52"/>
       <c r="N74" s="53"/>
@@ -3182,7 +3182,7 @@
         <v>98</v>
       </c>
       <c r="C76" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76" s="2"/>
       <c r="G76" s="53"/>
@@ -3212,7 +3212,7 @@
         <v>99</v>
       </c>
       <c r="C78" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D78" s="2"/>
       <c r="G78" s="52"/>
@@ -3239,7 +3239,7 @@
         <v>99</v>
       </c>
       <c r="F80" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N80" s="53"/>
       <c r="O80" s="23"/>
@@ -3268,12 +3268,12 @@
       </c>
       <c r="D82" s="2"/>
       <c r="O82" s="67" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="P82" s="67"/>
       <c r="Q82" s="67"/>
       <c r="R82" s="27">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3360,7 +3360,7 @@
         <v>46</v>
       </c>
       <c r="I89" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N89" s="40"/>
     </row>
@@ -3397,10 +3397,10 @@
       <c r="B92" s="51"/>
       <c r="C92" s="51"/>
       <c r="E92" s="19" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F92" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" s="53"/>
       <c r="N92" s="40"/>
@@ -3422,7 +3422,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D94" s="2"/>
       <c r="K94" s="57" t="s">
@@ -3489,7 +3489,7 @@
         <v>24</v>
       </c>
       <c r="F99" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" s="52"/>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="F102" s="51"/>
       <c r="H102" s="19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I102" s="13">
         <v>1</v>
@@ -3536,7 +3536,7 @@
         <v>102</v>
       </c>
       <c r="C103" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D103" s="2"/>
       <c r="G103" s="52"/>
@@ -3556,10 +3556,10 @@
       <c r="B105" s="50"/>
       <c r="C105" s="50"/>
       <c r="E105" s="19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F105" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3577,7 +3577,7 @@
         <v>103</v>
       </c>
       <c r="C107" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D107" s="2"/>
     </row>
